--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260916.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260916.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>15.03%</t>
+          <t>15.44%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>686,810,000</t>
+          <t>689,610,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>12.26%</t>
+          <t>12.77%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>915,097,000</t>
+          <t>921,857,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>10.35%</t>
+          <t>10.74%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>179,850,000</t>
+          <t>180,670,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>9.72%</t>
+          <t>10.12%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>8.87%</t>
+          <t>9.20%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.85%</t>
+          <t>6.01%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>5.36%</t>
+          <t>5.58%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.79%</t>
+          <t>3.94%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.32%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.77%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>139,840,000</t>
+          <t>140,080,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>2.05%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>251,824,000</t>
+          <t>253,824,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
@@ -902,24 +902,24 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.34%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>209,810,000</t>
+          <t>64,910,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -931,22 +931,22 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>64,910,000</t>
+          <t>209,810,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>103,700,000</t>
+          <t>105,200,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
@@ -1056,73 +1056,73 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>正新</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>119,660,000</t>
+          <t>35,270,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>興富發</t>
+          <t>正新</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>77,000,000</t>
+          <t>119,660,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>興富發</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>35,270,000</t>
+          <t>77,000,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
@@ -1144,51 +1144,51 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>12,488,000</t>
+          <t>40,513,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>39,933,000</t>
+          <t>12,488,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>13,510,000</t>
+          <t>13,810,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
@@ -1298,24 +1298,24 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>27,940,000</t>
+          <t>8,070,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,39 +1327,39 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>41,500,000</t>
+          <t>27,940,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>8,060,000</t>
+          <t>41,500,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1393,39 +1393,39 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>材料*-KY</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>41,500,000</t>
+          <t>15,520,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.33%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>材料*-KY</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>29,096,000</t>
+          <t>41,500,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>15,520,000</t>
+          <t>29,096,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1481,35 +1481,39 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>B20258</t>
+          <t>202610TX</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>P14台泥1A</t>
+          <t>台指期</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>760,000,000</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr"/>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>0.04%</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>B402BR</t>
+          <t>B20258</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>P14台塑1</t>
+          <t>P14台泥1A</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>760,000,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr"/>
@@ -1517,17 +1521,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>B618CS</t>
+          <t>B402BR</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>P10台積6A</t>
+          <t>P14台塑1</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>160,000,000</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr"/>
@@ -1535,17 +1539,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>B644B6</t>
+          <t>B618CS</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>P07鴻海1E</t>
+          <t>P10台積6A</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>66,000,000</t>
+          <t>160,000,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr"/>
@@ -1553,17 +1557,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>B801AE</t>
+          <t>B618CZ</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>02中鋼1C</t>
+          <t>P11台積2C</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>110,000,000</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr"/>
@@ -1571,17 +1575,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>B903ZC</t>
+          <t>B644B6</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>P12台電6A</t>
+          <t>P07鴻海1E</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>50,000,000</t>
+          <t>66,000,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr"/>
@@ -1589,17 +1593,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>B92365</t>
+          <t>B718A9</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>P14遠鼎2B</t>
+          <t>P12中油1A</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>160,000,000</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr"/>
@@ -1607,17 +1611,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>B92603</t>
+          <t>B801AE</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>P13永昌證1</t>
+          <t>02中鋼1C</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>119,000,000</t>
+          <t>210,000,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr"/>
@@ -1625,17 +1629,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>B95146</t>
+          <t>B801AU</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>P14中租1A</t>
+          <t>P14中鋼2</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>300,000,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr"/>
@@ -1643,17 +1647,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>B95459</t>
+          <t>B86912</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>P09中控2C</t>
+          <t>P14和潤2A</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>400,000,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr"/>
@@ -1661,17 +1665,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>B96524</t>
+          <t>B903ZC</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>P11元金1</t>
+          <t>P12台電6A</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>150,000,000</t>
+          <t>50,000,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1679,17 +1683,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>B98412</t>
+          <t>B92365</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>P11奇美1</t>
+          <t>P14遠鼎2B</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>105,000,000</t>
+          <t>160,000,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
@@ -1697,17 +1701,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>B98907</t>
+          <t>B92603</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>P09國泰金2</t>
+          <t>P13永昌證1</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>400,000,000</t>
+          <t>119,000,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
@@ -1715,17 +1719,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>B98914</t>
+          <t>B95146</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>P12國泰金1B</t>
+          <t>P14中租1A</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>50,000,000</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
@@ -1733,12 +1737,12 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>B99503</t>
+          <t>B95459</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>P12富壽1A</t>
+          <t>P09中控2C</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -1751,17 +1755,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>B99607</t>
+          <t>B96524</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>P13國壽1A</t>
+          <t>P11元金1</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>200,000,000</t>
+          <t>150,000,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr"/>
@@ -1769,17 +1773,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>B9A609</t>
+          <t>B98412</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>P13元大證1</t>
+          <t>P11奇美1</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>105,000,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr"/>
@@ -1787,17 +1791,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>B98610</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>P13玉控1</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>14,678,931,081</t>
+          <t>52,000,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr"/>
@@ -1805,17 +1809,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>G10323</t>
+          <t>B98907</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>P14高銀2</t>
+          <t>P09國泰金2</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>30,000,000</t>
+          <t>400,000,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr"/>
@@ -1823,12 +1827,12 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>G107CP</t>
+          <t>B98914</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>P15北富銀1A</t>
+          <t>P12國泰金1B</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -1841,17 +1845,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>G11748</t>
+          <t>B98915</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>P15王道銀1A</t>
+          <t>P13國泰金1</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>60,000,000</t>
+          <t>206,000,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr"/>
@@ -1859,17 +1863,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>G139AL</t>
+          <t>B99503</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>P13遠銀1A</t>
+          <t>P12富壽1A</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr"/>
@@ -1877,17 +1881,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>G139AN</t>
+          <t>B99509</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>P14遠銀1</t>
+          <t>P13富壽2A</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>240,000,000</t>
+          <t>30,000,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr"/>
@@ -1895,17 +1899,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>B99607</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>P13國壽1A</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>2,147,934,603</t>
+          <t>200,000,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr"/>
@@ -1913,20 +1917,200 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
+          <t>B99907</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>P12合迪1B</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>50,000,000</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>B9A609</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>P13元大證1</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>10,000,000</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>B9AK02</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>P12凱基壽1</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>22,000,000</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>CASH</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>15,834,929,202</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>G10323</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>P14高銀2</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>30,000,000</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>G107CP</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>P15北富銀1A</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>50,000,000</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>G11748</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>P15王道銀1A</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>60,000,000</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>G139AL</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>P13遠銀1A</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>10,000,000</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>G139AN</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>P14遠銀1</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>240,000,000</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>M_NTD</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>MARGIN</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>2,148,050,191</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
           <t>RDI_NTD</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
         </is>
       </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>-844,482,411</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="inlineStr"/>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>-2,201,882,535</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
